--- a/tonalzone_master_products_template.xlsx
+++ b/tonalzone_master_products_template.xlsx
@@ -2568,7 +2568,7 @@
         <v>NEUTRAL</v>
       </c>
       <c r="N49" t="str">
-        <v>https://cdn.shopify.com/s/files/1/0040/7201/3924/files/3_1_3131f003-c9bc-4489-b36c-c39a9593e677.jpg?v=1708683816</v>
+        <v>https://www.headphonezone.in/cdn/shop/files/Headphone-zone-ooopusX-Op-22-Gallary-030.jpg?v=1785913287&amp;width=800</v>
       </c>
     </row>
     <row r="50">
